--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104493_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104493_W4.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.443</v>
+        <v>6.5338</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4927</v>
+        <v>5.4611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9503</v>
+        <v>1.0728</v>
       </c>
       <c r="G2" t="n">
-        <v>4.208</v>
+        <v>4.2049</v>
       </c>
       <c r="H2" t="n">
-        <v>1.785</v>
+        <v>1.7782</v>
       </c>
       <c r="I2" t="n">
-        <v>2.423</v>
+        <v>2.4268</v>
       </c>
       <c r="J2" t="n">
-        <v>4.887</v>
+        <v>4.8595</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2672</v>
+        <v>1.2476</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6197</v>
+        <v>3.612</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.6546</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2187</v>
+        <v>-0.1264</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4869</v>
+        <v>-0.4879</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2683</v>
+        <v>0.3616</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0203</v>
+        <v>3.8749</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9371</v>
+        <v>2.685</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0832</v>
+        <v>1.1898</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2276</v>
+        <v>-0.224</v>
       </c>
       <c r="H3" t="n">
+        <v>0.6401</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.8641</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.8573</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.909</v>
+      </c>
+      <c r="M3" t="n">
         <v>0.6333</v>
       </c>
-      <c r="I3" t="n">
-        <v>-0.861</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-0.8491</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.901</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.6214</v>
-      </c>
       <c r="N3" t="n">
-        <v>0.5814</v>
+        <v>0.5884</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5163</v>
+        <v>0.3752</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5081</v>
+        <v>0.2739</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1013</v>
       </c>
       <c r="V3" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W3" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.492</v>
+        <v>3.355</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7546</v>
+        <v>3.3339</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2626</v>
+        <v>0.0211</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4095</v>
+        <v>2.4143</v>
       </c>
       <c r="H4" t="n">
-        <v>2.111</v>
+        <v>2.1164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2985</v>
+        <v>0.2979</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1043</v>
+        <v>3.0833</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7663</v>
+        <v>1.7582</v>
       </c>
       <c r="L4" t="n">
-        <v>1.338</v>
+        <v>1.3252</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6948</v>
+        <v>-0.669</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5873</v>
+        <v>0.4367</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8771</v>
+        <v>0.4782</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2898</v>
+        <v>-0.0414</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6537</v>
+        <v>2.8809</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3668</v>
+        <v>1.8068</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.713</v>
+        <v>1.0742</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0158</v>
+        <v>-0.7441</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5222</v>
+        <v>1.7917</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5064</v>
+        <v>-2.5358</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3141</v>
+        <v>-0.6343</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5629</v>
+        <v>0.9308</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7512</v>
+        <v>-1.5651</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.2983</v>
+        <v>-0.1099</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0407</v>
+        <v>0.8609</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.2576</v>
+        <v>-0.9708</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4773</v>
+        <v>0.3079</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1603</v>
+        <v>0.1043</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3169</v>
+        <v>0.2036</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7071</v>
+        <v>2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>2.3367</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2026</v>
+        <v>2.6773</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2507</v>
+        <v>4.2885</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9518</v>
+        <v>-1.6112</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.741</v>
+        <v>1.027</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7834</v>
+        <v>1.5304</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.5243</v>
+        <v>-0.5034</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6084000000000001</v>
+        <v>4.2935</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9351</v>
+        <v>2.5511</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.5435</v>
+        <v>1.7425</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1326</v>
+        <v>-3.2665</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8483000000000001</v>
+        <v>-1.0207</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9808</v>
+        <v>-2.2458</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3759</v>
+        <v>0.4926</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4869</v>
+        <v>0.1136</v>
       </c>
       <c r="U6" t="n">
-        <v>0.111</v>
+        <v>0.379</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1853</v>
+        <v>0.7025</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3461</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7872</v>
+        <v>1.6408</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3276</v>
+        <v>2.688</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5404</v>
+        <v>-1.0472</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4412</v>
+        <v>1.4446</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5873</v>
+        <v>2.5823</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1461</v>
+        <v>-1.1377</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1624</v>
+        <v>3.1482</v>
       </c>
       <c r="K7" t="n">
-        <v>3.0131</v>
+        <v>2.9992</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7212</v>
+        <v>-1.7036</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3046</v>
+        <v>0.1476</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6079</v>
+        <v>-0.2325</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9125</v>
+        <v>0.3801</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.286</v>
+        <v>0.9304</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2985</v>
+        <v>2.2643</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9875</v>
+        <v>-1.3339</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6543</v>
+        <v>-0.3461</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3851</v>
+        <v>-0.477</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2692</v>
+        <v>0.131</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1151</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.71</v>
+        <v>-0.376</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4051</v>
+        <v>1.1467</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5392</v>
+        <v>-1.1168</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6751</v>
+        <v>-0.1011</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1359</v>
+        <v>-1.0157</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8171</v>
+        <v>0.5936</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3176</v>
+        <v>0.4041</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4995</v>
+        <v>0.1895</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.358</v>
+        <v>0.5756</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8065</v>
+        <v>0.1159</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4484</v>
+        <v>0.4597</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3488</v>
+        <v>1.6649</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.482</v>
+        <v>1.3953</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1333</v>
+        <v>0.2696</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7834</v>
+        <v>1.101</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3708</v>
+        <v>0.7067</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1541</v>
+        <v>0.3943</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1321</v>
+        <v>0.5639</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1113</v>
+        <v>0.6886</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0209</v>
+        <v>-0.1246</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0263</v>
+        <v>1.0897</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0696</v>
+        <v>0.1531</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0959</v>
+        <v>0.9366</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2445</v>
+        <v>0.1259</v>
       </c>
       <c r="E10" t="n">
-        <v>0.457</v>
+        <v>0.6146</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7016</v>
+        <v>-0.4886</v>
       </c>
       <c r="G10" t="n">
-        <v>2.263</v>
+        <v>2.2661</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4501</v>
+        <v>1.4558</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8102</v>
       </c>
       <c r="J10" t="n">
-        <v>3.0965</v>
+        <v>3.0814</v>
       </c>
       <c r="K10" t="n">
-        <v>1.42</v>
+        <v>1.4134</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8335</v>
+        <v>-0.8154</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0556</v>
+        <v>0.4321</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3297</v>
+        <v>-0.1418</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3853</v>
+        <v>0.574</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2949</v>
+        <v>-0.2748</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4621</v>
+        <v>0.363</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.757</v>
+        <v>-0.6378</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4075</v>
+        <v>2.3988</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4373</v>
+        <v>1.4307</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9702</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2191</v>
+        <v>4.1878</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2094</v>
+        <v>2.1923</v>
       </c>
       <c r="L11" t="n">
-        <v>2.0097</v>
+        <v>1.9955</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8116</v>
+        <v>-1.789</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2199</v>
+        <v>0.266</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2994</v>
+        <v>0.253</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0796</v>
+        <v>0.013</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1904</v>
+        <v>-1.5498</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1773</v>
+        <v>-0.5212</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0131</v>
+        <v>-1.0285</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.267</v>
+        <v>-2.2688</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0361</v>
+        <v>0.0373</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.303</v>
+        <v>-2.3061</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4071</v>
+        <v>-0.4189</v>
       </c>
       <c r="K12" t="n">
-        <v>1.091</v>
+        <v>1.0859</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8599</v>
+        <v>-1.8499</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0549</v>
+        <v>-1.0487</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7836</v>
+        <v>0.4215</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4567</v>
+        <v>0.1253</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3269</v>
+        <v>0.2962</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8706</v>
+        <v>-3.4138</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8212</v>
+        <v>-4.5424</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9506</v>
+        <v>1.1286</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4333</v>
+        <v>-2.4279</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1442</v>
+        <v>0.1491</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5776</v>
+        <v>-2.577</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9035</v>
+        <v>-1.9152</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4054</v>
+        <v>-0.4104</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5299</v>
+        <v>-0.5127</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5496</v>
+        <v>0.5595</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7153</v>
+        <v>-0.2543</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6079</v>
+        <v>-0.3022</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1074</v>
+        <v>0.0479</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>16.64240000000001</v>
+        <v>17.3562</v>
       </c>
       <c r="E14" t="n">
-        <v>18.1551</v>
+        <v>18.5575</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.512699999999999</v>
+        <v>-1.201</v>
       </c>
       <c r="G14" t="n">
-        <v>9.381600000000002</v>
+        <v>9.409699999999997</v>
       </c>
       <c r="H14" t="n">
-        <v>14.393</v>
+        <v>14.4303</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.011200000000001</v>
+        <v>-5.0204</v>
       </c>
       <c r="J14" t="n">
-        <v>20.9138</v>
+        <v>20.6997</v>
       </c>
       <c r="K14" t="n">
-        <v>14.2508</v>
+        <v>14.1505</v>
       </c>
       <c r="L14" t="n">
-        <v>6.662900000000001</v>
+        <v>6.549400000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.5322</v>
+        <v>-11.2902</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1421000000000004</v>
+        <v>0.2796000000000002</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.6744</v>
+        <v>-11.5696</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.134</v>
+        <v>-1.138</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.7441</v>
+        <v>-14.7961</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6102</v>
+        <v>13.6582</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4781</v>
+        <v>4.182200000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.03029999999999977</v>
+        <v>0.7410999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4477</v>
+        <v>3.441399999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9171</v>
+        <v>4.902600000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>11.9554</v>
+        <v>11.9128</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.0382</v>
+        <v>-7.010199999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3687</v>
+        <v>4.8162</v>
       </c>
       <c r="E15" t="n">
-        <v>7.2481</v>
+        <v>7.1892</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8795</v>
+        <v>-2.3729</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4071</v>
+        <v>5.3889</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6377</v>
+        <v>-1.6398</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0449</v>
+        <v>7.0288</v>
       </c>
       <c r="J15" t="n">
-        <v>9.209</v>
+        <v>9.158099999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0075</v>
+        <v>0.989</v>
       </c>
       <c r="L15" t="n">
-        <v>8.201599999999999</v>
+        <v>8.1691</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.8019</v>
+        <v>-3.7692</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6452</v>
+        <v>-2.6288</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1567</v>
+        <v>-1.1403</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6775</v>
+        <v>-0.2069</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2389</v>
+        <v>-0.2374</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4386</v>
+        <v>0.0305</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3943</v>
+        <v>2.3057</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.081</v>
+        <v>0.3718</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4753</v>
+        <v>1.934</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9667</v>
+        <v>0.969</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4242</v>
+        <v>-1.4218</v>
       </c>
       <c r="I16" t="n">
-        <v>2.391</v>
+        <v>2.3908</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8648</v>
+        <v>0.8528</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5646</v>
+        <v>1.5563</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1019</v>
+        <v>0.1162</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1187</v>
+        <v>-0.208</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9043</v>
+        <v>-0.4324</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2144</v>
+        <v>0.2243</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.499</v>
+        <v>0.9387</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3169</v>
+        <v>0.2176</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8159</v>
+        <v>0.7211</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0859</v>
+        <v>0.0756</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0603</v>
+        <v>-1.0762</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1462</v>
+        <v>1.1517</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0794</v>
+        <v>1.046</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6345</v>
+        <v>-0.6592</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9935</v>
+        <v>-0.9704</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9575</v>
+        <v>-0.4947</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8861</v>
+        <v>-0.2954</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.1994</v>
       </c>
       <c r="V17" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>M. ALLEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.288</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4994</v>
+        <v>1.4238</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2114</v>
+        <v>-2.0422</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1257</v>
+        <v>0.8935</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1284</v>
+        <v>1.6575</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0027</v>
+        <v>-0.764</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4654</v>
+        <v>1.4367</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3881</v>
+        <v>2.1891</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.7524</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6603</v>
+        <v>-0.5432</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.5315</v>
       </c>
       <c r="O18" t="n">
-        <v>0.08</v>
+        <v>-0.0116</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9185</v>
+        <v>-0.7003</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9648</v>
+        <v>-0.5576</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0463</v>
+        <v>-0.1427</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.9497</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ALLEN</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7845</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>1.44</v>
+        <v>-0.2155</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2245</v>
+        <v>-0.407</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8962</v>
+        <v>-1.1183</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6638</v>
+        <v>-1.126</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7675999999999999</v>
+        <v>0.0077</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4502</v>
+        <v>-0.4753</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1992</v>
+        <v>-0.3932</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.749</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.554</v>
+        <v>-0.643</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5354</v>
+        <v>-0.7328</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0186</v>
+        <v>0.0898</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8544</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5565</v>
+        <v>0.2598</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2979</v>
+        <v>-0.268</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.9604</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.5068</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4765</v>
+        <v>-1.7613</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7078</v>
+        <v>-1.9909</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2313</v>
+        <v>0.2296</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.3926</v>
+        <v>-3.407</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.9071</v>
+        <v>-3.9333</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5145</v>
+        <v>0.5264</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7651</v>
+        <v>-1.8035</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.4741</v>
+        <v>-2.511</v>
       </c>
       <c r="L20" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6275</v>
+        <v>-1.6034</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.433</v>
+        <v>-1.4223</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1766</v>
+        <v>-0.4438</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4476</v>
+        <v>-0.6834</v>
       </c>
       <c r="U20" t="n">
-        <v>0.271</v>
+        <v>0.2396</v>
       </c>
       <c r="V20" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W20" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6938</v>
+        <v>-3.6273</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8135</v>
+        <v>-0.828</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8802</v>
+        <v>-2.7993</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5862</v>
+        <v>-2.5795</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0505</v>
+        <v>-2.0479</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5357</v>
+        <v>-0.5316</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0858</v>
+        <v>1.0769</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1456</v>
+        <v>-0.1519</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.672</v>
+        <v>-3.6565</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9048</v>
+        <v>-1.8961</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8807</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>-0.7667</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9695</v>
+        <v>-3.8877</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7042</v>
+        <v>-2.9598</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2653</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.0901</v>
+        <v>-5.0918</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.5627</v>
+        <v>-3.5587</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5274</v>
+        <v>-1.5331</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4472</v>
+        <v>-2.467</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4688</v>
+        <v>-1.4759</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9784</v>
+        <v>-0.9912</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6429</v>
+        <v>-2.6248</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0939</v>
+        <v>-2.0829</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2404</v>
+        <v>-0.1617</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2571</v>
+        <v>-0.4928</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0166</v>
+        <v>0.3311</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1769</v>
+        <v>-4.0461</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1508</v>
+        <v>-1.2642</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.3277</v>
+        <v>-2.7819</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7951</v>
+        <v>-1.1482</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5526</v>
+        <v>0.6289</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2425</v>
+        <v>-1.7771</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7602</v>
+        <v>-0.5485</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1354</v>
+        <v>0.8446</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8956</v>
+        <v>-1.3931</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5552</v>
+        <v>-0.5997</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4171</v>
+        <v>-0.2157</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1381</v>
+        <v>-0.384</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1342</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1476</v>
+        <v>0.0338</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2299</v>
+        <v>0.2647</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0823</v>
+        <v>-0.2309</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.6636</v>
+        <v>-2.0212</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.8243</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.54</v>
+        <v>-4.2159</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4826</v>
+        <v>1.0164</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0574</v>
+        <v>-5.2323</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5977</v>
+        <v>-1.7915</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3608</v>
+        <v>-1.5565</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2369</v>
+        <v>-0.235</v>
       </c>
       <c r="J24" t="n">
-        <v>2.2979</v>
+        <v>0.7451</v>
       </c>
       <c r="K24" t="n">
-        <v>1.749</v>
+        <v>-0.1486</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.8937</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.8956</v>
+        <v>-2.5365</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.1098</v>
+        <v>-1.4078</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.7858</v>
+        <v>-1.1287</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8308</v>
+        <v>0.0929</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.378</v>
+        <v>0.1136</v>
       </c>
       <c r="U24" t="n">
-        <v>1.2088</v>
+        <v>-0.0207</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1853</v>
+        <v>-3.6554</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5513</v>
+        <v>-5.1512</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7197</v>
+        <v>-1.7593</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8315</v>
+        <v>-3.3919</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.1502</v>
+        <v>-1.6005</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6277</v>
+        <v>-0.3564</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7779</v>
+        <v>-1.2442</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5376</v>
+        <v>2.2688</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8485</v>
+        <v>1.7409</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3861</v>
+        <v>0.5279</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6126</v>
+        <v>-3.8693</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2209</v>
+        <v>-2.0973</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3918</v>
+        <v>-1.772</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4691</v>
+        <v>0.2217</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2087</v>
+        <v>-0.6137</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2604</v>
+        <v>0.8353</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.0246</v>
+        <v>-2.1789</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.6425</v>
+        <v>-15.8698</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5126</v>
+        <v>1.201100000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-18.155</v>
+        <v>-17.0707</v>
       </c>
       <c r="G26" t="n">
-        <v>-9.381699999999999</v>
+        <v>-9.409800000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>-14.3928</v>
+        <v>-14.4302</v>
       </c>
       <c r="I26" t="n">
-        <v>5.011299999999999</v>
+        <v>5.020400000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>11.532</v>
+        <v>11.2901</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1421000000000001</v>
+        <v>-0.2797000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>11.6743</v>
+        <v>11.5697</v>
       </c>
       <c r="M26" t="n">
-        <v>-20.9136</v>
+        <v>-20.6998</v>
       </c>
       <c r="N26" t="n">
-        <v>-14.2508</v>
+        <v>-14.1505</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.6629</v>
+        <v>-6.5492</v>
       </c>
       <c r="P26" t="n">
-        <v>1.1344</v>
+        <v>1.1384</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.6101</v>
+        <v>-13.6581</v>
       </c>
       <c r="R26" t="n">
-        <v>14.7441</v>
+        <v>14.7961</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.478</v>
+        <v>-2.6953</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.4477</v>
+        <v>-3.4413</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.03040000000000004</v>
+        <v>0.7457000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.9169</v>
+        <v>-4.9026</v>
       </c>
       <c r="W26" t="n">
-        <v>7.0381</v>
+        <v>7.0101</v>
       </c>
       <c r="X26" t="n">
-        <v>-11.9551</v>
+        <v>-11.9128</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104493_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104493_W4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.010199999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104493_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-11.9128</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
